--- a/src/attributions/attributions_saliency_traj_484.xlsx
+++ b/src/attributions/attributions_saliency_traj_484.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG5"/>
+  <dimension ref="A1:GG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,1709 +1568,6261 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.4560750126838684</v>
+        <v>0.008003714494407177</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2015168815851212</v>
+        <v>0.0006600705673918128</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05968505889177322</v>
+        <v>0.000899441190995276</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03176242858171463</v>
+        <v>0.00188167963642627</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09491648524999619</v>
+        <v>0.003533140057697892</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07713378220796585</v>
+        <v>0.001648523146286607</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09352665394544601</v>
+        <v>0.0002221354079665616</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00820388738065958</v>
+        <v>0.00485899718478322</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05947276949882507</v>
+        <v>0.0002980384160764515</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4231305122375488</v>
+        <v>0.008393354713916779</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01959259808063507</v>
+        <v>0.003071258310228586</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09222669154405594</v>
+        <v>0.001049644080922008</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07587901502847672</v>
+        <v>0.004474354442209005</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2329255044460297</v>
+        <v>0.002228958532214165</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2165298461914062</v>
+        <v>0.0008435177733190358</v>
       </c>
       <c r="P3" t="n">
-        <v>0.170661985874176</v>
+        <v>0.001372355036437511</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.06532009690999985</v>
+        <v>0.004620886407792568</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1326940953731537</v>
+        <v>0.001122449524700642</v>
       </c>
       <c r="S3" t="n">
-        <v>0.04875124990940094</v>
+        <v>0.0002954590308945626</v>
       </c>
       <c r="T3" t="n">
-        <v>0.01920985616743565</v>
+        <v>0.0005654385895468295</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0565415732562542</v>
+        <v>0.0009916443377733231</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01480170525610447</v>
+        <v>0.0005913304630666971</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2536489069461823</v>
+        <v>0.001256734016351402</v>
       </c>
       <c r="X3" t="n">
-        <v>0.005377499386668205</v>
+        <v>0.0003905102203134447</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1479622274637222</v>
+        <v>0.0008067567832767963</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1076676249504089</v>
+        <v>0.0001275479880860075</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.04941187053918839</v>
+        <v>0.0002461711701471359</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02963403053581715</v>
+        <v>0.001571736298501492</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.005494258366525173</v>
+        <v>0.0001741843589115888</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.03076454997062683</v>
+        <v>0.0003607060643844306</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.02167503535747528</v>
+        <v>0.003159145126119256</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.213190570473671</v>
+        <v>0.001109780976548791</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.03987713903188705</v>
+        <v>0.001449401839636266</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.08223292231559753</v>
+        <v>0.001917357323691249</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.1240112856030464</v>
+        <v>0.002100437181070447</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.06845451146364212</v>
+        <v>0.000114400580059737</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.1185920313000679</v>
+        <v>0.0009650338906794786</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.05458251759409904</v>
+        <v>0.002124155638739467</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.06370669603347778</v>
+        <v>0.0005637342692352831</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.09852209687232971</v>
+        <v>0.0006764121353626251</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1467992216348648</v>
+        <v>0.0007973642204888165</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.05788886919617653</v>
+        <v>0.0005376487970352173</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.07376464456319809</v>
+        <v>0.0004444832738954574</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.01868821494281292</v>
+        <v>0.000591861258726567</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.02147957310080528</v>
+        <v>0.0005628298968076706</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.2621770799160004</v>
+        <v>0.004837042186409235</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.11387600004673</v>
+        <v>0.001900821691378951</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.01374950166791677</v>
+        <v>0.001776102348230779</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.1088069826364517</v>
+        <v>0.001234296476468444</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.004862068220973015</v>
+        <v>0.0006603190558962524</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.04667983204126358</v>
+        <v>0.001084105693735182</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1340956836938858</v>
+        <v>0.001479823142290115</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.0465199314057827</v>
+        <v>0.00198565935716033</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.006712302565574646</v>
+        <v>0.0001933820603881031</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.105413094162941</v>
+        <v>0.0009032812668010592</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1947290152311325</v>
+        <v>0.0005520296399481595</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.08682336658239365</v>
+        <v>0.0001272485387744382</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2411367744207382</v>
+        <v>3.895227564498782e-06</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.04384223744273186</v>
+        <v>0.003156657796353102</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.05182062834501266</v>
+        <v>0.001412269193679094</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.1314884722232819</v>
+        <v>0.0001372983533656225</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.1832874417304993</v>
+        <v>0.0001238487893715501</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.07873570173978806</v>
+        <v>0.001145398826338351</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.02850467711687088</v>
+        <v>0.00221900874748826</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1368229240179062</v>
+        <v>0.0004701569851022214</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1093301996588707</v>
+        <v>0.001338692731224</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.05064977705478668</v>
+        <v>0.002892258111387491</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1280783414840698</v>
+        <v>0.001874792273156345</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.1605179607868195</v>
+        <v>0.0002925894514191896</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001697495463304222</v>
+        <v>0.0004454329609870911</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0480230338871479</v>
+        <v>0.001593619817867875</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.01096084527671337</v>
+        <v>7.386262586805969e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1642633825540543</v>
+        <v>0.00207634549587965</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.01866883412003517</v>
+        <v>0.0004457150353118777</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.02242847345769405</v>
+        <v>0.002496737986803055</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1378691792488098</v>
+        <v>0.0005936635425314307</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1584346443414688</v>
+        <v>6.447639316320419e-05</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.00227908231317997</v>
+        <v>0.0005965224700048566</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.02239724434912205</v>
+        <v>0.0004691174253821373</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0131048234179616</v>
+        <v>0.0009856187971308827</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.04346740990877151</v>
+        <v>0.001377049251459539</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.08663174510002136</v>
+        <v>0.002013053745031357</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.08356592059135437</v>
+        <v>0.0006853446830064058</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.008148832246661186</v>
+        <v>0.0001392885460518301</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.07413829863071442</v>
+        <v>0.0008510394836775959</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.01219504233449697</v>
+        <v>8.584640454500914e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.04741643369197845</v>
+        <v>8.663651533424854e-05</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.01131546124815941</v>
+        <v>0.0008767901454120874</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.1047759428620338</v>
+        <v>0.0005682061309926212</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.0006848378106951714</v>
+        <v>4.870379052590579e-05</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.05360043793916702</v>
+        <v>0.0003930823877453804</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.002840702421963215</v>
+        <v>0.002404418075457215</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1002050489187241</v>
+        <v>0.001871114363893867</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.02397168427705765</v>
+        <v>0.002960046986117959</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1230449378490448</v>
+        <v>0.000216088374145329</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.1503826677799225</v>
+        <v>0.0007750891381874681</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.02872005850076675</v>
+        <v>0.003944858908653259</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.07924236357212067</v>
+        <v>0.004824407398700714</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.001969832926988602</v>
+        <v>0.0003139259642921388</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.08097158372402191</v>
+        <v>0.001941423746757209</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.08352868258953094</v>
+        <v>0.001311691245064139</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.004436676856130362</v>
+        <v>4.563092807075009e-05</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.03533191233873367</v>
+        <v>0.0007857684977352619</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.01091033685952425</v>
+        <v>0.0004875591257587075</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01827625371515751</v>
+        <v>3.649204154498875e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.003183342516422272</v>
+        <v>0.0005666111246682703</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.09795811772346497</v>
+        <v>0.0002045191795332357</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.02356606721878052</v>
+        <v>2.883211527660023e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1067397892475128</v>
+        <v>0.001069549471139908</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.02903085947036743</v>
+        <v>0.004966766573488712</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.01859722845256329</v>
+        <v>0.0007167733856476843</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.2704220712184906</v>
+        <v>0.0006949733360670507</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.01017681043595076</v>
+        <v>0.0008215581765398383</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.1621051728725433</v>
+        <v>0.001942182774655521</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.09402310848236084</v>
+        <v>7.211667252704501e-06</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.1312518268823624</v>
+        <v>0.0004380065947771072</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.01343795657157898</v>
+        <v>0.001843811944127083</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.07032401859760284</v>
+        <v>0.001448005205020308</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.00214864406734705</v>
+        <v>0.001416565501131117</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.01312855165451765</v>
+        <v>0.0001755414123181254</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.03607120364904404</v>
+        <v>0.0001408607058692724</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.03803456574678421</v>
+        <v>0.001275843009352684</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.06779889762401581</v>
+        <v>0.0002841332461684942</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1250383108854294</v>
+        <v>0.0008722792845219374</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.1724496185779572</v>
+        <v>0.001138841267675161</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.03049484267830849</v>
+        <v>0.0001597006630618125</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.04653691127896309</v>
+        <v>0.0008254036074504256</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1597563922405243</v>
+        <v>7.232144707813859e-05</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.03676895052194595</v>
+        <v>0.0009216860053129494</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.08059293031692505</v>
+        <v>0.001283621415495872</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.1346737295389175</v>
+        <v>0.0008554009255021811</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.04352656379342079</v>
+        <v>0.0009637810871936381</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.0124308867380023</v>
+        <v>0.0003225677646696568</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.1502916067838669</v>
+        <v>0.0007642714772373438</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.02738695777952671</v>
+        <v>0.000624869717285037</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.08180833607912064</v>
+        <v>0.001168338116258383</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.08520032465457916</v>
+        <v>0.0004576285718940198</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.02352778241038322</v>
+        <v>0.0005039359675720334</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.05122272297739983</v>
+        <v>0.00108441011980176</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0478523001074791</v>
+        <v>2.431223401799798e-05</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.008414514362812042</v>
+        <v>0.0004451182321645319</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.01864870078861713</v>
+        <v>0.001537674223072827</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.03179421648383141</v>
+        <v>0.001154482248239219</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.007849136367440224</v>
+        <v>0.0004531932936515659</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.1067899242043495</v>
+        <v>0.00072785175871104</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0432719960808754</v>
+        <v>0.002418716438114643</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.06390555948019028</v>
+        <v>0.0001324969489360228</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.01913750544190407</v>
+        <v>0.001835108152590692</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.07683516293764114</v>
+        <v>0.000155293382704258</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.01522262208163738</v>
+        <v>0.0006170118576847017</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.08989981561899185</v>
+        <v>0.0003099965397268534</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.1124937534332275</v>
+        <v>0.0009353444329462945</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.05800182744860649</v>
+        <v>0.0009913954418152571</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.09613862633705139</v>
+        <v>0.001772750169038773</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.04810409247875214</v>
+        <v>0.001379474531859159</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.007483203895390034</v>
+        <v>0.0003229330759495497</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.05300061777234077</v>
+        <v>0.0001970925077330321</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.006502010859549046</v>
+        <v>0.0001155152567662299</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.04288805276155472</v>
+        <v>0.0002458535600453615</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.01277133822441101</v>
+        <v>0.001027500489726663</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.1031253188848495</v>
+        <v>0.0008807356934994459</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.02055852860212326</v>
+        <v>0.0003753950004465878</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.105305552482605</v>
+        <v>0.004247679375112057</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.09735122323036194</v>
+        <v>0.0005974803934805095</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.08861087262630463</v>
+        <v>0.000520810775924474</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.03787169605493546</v>
+        <v>0.003060830757021904</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.07042562216520309</v>
+        <v>0.0004529731813818216</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.007170828059315681</v>
+        <v>2.715230220928788e-05</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.03570301830768585</v>
+        <v>0.001415944891050458</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.02329013124108315</v>
+        <v>0.001283952267840505</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.0103633850812912</v>
+        <v>0.0001581936667207628</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2134477347135544</v>
+        <v>0.001331800827756524</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.06917743384838104</v>
+        <v>0.004071756731718779</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0250705499202013</v>
+        <v>0.002374636707827449</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.1091957464814186</v>
+        <v>0.006562414579093456</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.2183631062507629</v>
+        <v>0.003798605408519506</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.03213062882423401</v>
+        <v>0.001588881481438875</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.1170120164752007</v>
+        <v>0.0007908513071015477</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.005945848301053047</v>
+        <v>0.0007081121439114213</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.0123438760638237</v>
+        <v>0.0005804715328849852</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.02525599300861359</v>
+        <v>0.00227849674411118</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.001428760122507811</v>
+        <v>0.003423657733947039</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1094491183757782</v>
+        <v>0.0002901551779359579</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.05203170329332352</v>
+        <v>0.003537370357662439</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.1574185639619827</v>
+        <v>0.003523468971252441</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.07363683730363846</v>
+        <v>0.001930846832692623</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.01752600446343422</v>
+        <v>0.001244575716555119</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.1254563182592392</v>
+        <v>0.00236074416898191</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.09784843027591705</v>
+        <v>0.0003172532597091049</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2.499877155059949e-06</v>
+        <v>0.03153779730200768</v>
       </c>
       <c r="B4" t="n">
-        <v>6.38881658687751e-07</v>
+        <v>0.4579542279243469</v>
       </c>
       <c r="C4" t="n">
-        <v>7.030894835224899e-07</v>
+        <v>0.004860181361436844</v>
       </c>
       <c r="D4" t="n">
-        <v>2.078419925055641e-08</v>
+        <v>0.7006934881210327</v>
       </c>
       <c r="E4" t="n">
-        <v>2.833347707564826e-07</v>
+        <v>0.02853067964315414</v>
       </c>
       <c r="F4" t="n">
-        <v>7.99676769247526e-08</v>
+        <v>0.09921891242265701</v>
       </c>
       <c r="G4" t="n">
-        <v>1.200161932501942e-06</v>
+        <v>0.1278751194477081</v>
       </c>
       <c r="H4" t="n">
-        <v>5.715074848922086e-07</v>
+        <v>0.1815961599349976</v>
       </c>
       <c r="I4" t="n">
-        <v>9.901706334858318e-07</v>
+        <v>0.04621679335832596</v>
       </c>
       <c r="J4" t="n">
-        <v>2.282643890794134e-06</v>
+        <v>0.09917259216308594</v>
       </c>
       <c r="K4" t="n">
-        <v>5.754031917604152e-07</v>
+        <v>0.3592365980148315</v>
       </c>
       <c r="L4" t="n">
-        <v>5.381269261306443e-07</v>
+        <v>0.06462434679269791</v>
       </c>
       <c r="M4" t="n">
-        <v>9.601399142411537e-08</v>
+        <v>0.8956388235092163</v>
       </c>
       <c r="N4" t="n">
-        <v>8.530944910489779e-07</v>
+        <v>0.005132503807544708</v>
       </c>
       <c r="O4" t="n">
-        <v>1.178660085088268e-07</v>
+        <v>0.03428313136100769</v>
       </c>
       <c r="P4" t="n">
-        <v>1.243577912646288e-06</v>
+        <v>0.211966261267662</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.011666086014884e-06</v>
+        <v>0.03608548268675804</v>
       </c>
       <c r="R4" t="n">
-        <v>1.199554731101671e-06</v>
+        <v>0.001767273992300034</v>
       </c>
       <c r="S4" t="n">
-        <v>2.128260234712798e-08</v>
+        <v>0.01503127068281174</v>
       </c>
       <c r="T4" t="n">
-        <v>5.755265419793432e-07</v>
+        <v>0.05876853317022324</v>
       </c>
       <c r="U4" t="n">
-        <v>8.805251354715438e-07</v>
+        <v>0.07216278463602066</v>
       </c>
       <c r="V4" t="n">
-        <v>5.568649612541776e-07</v>
+        <v>0.02397882007062435</v>
       </c>
       <c r="W4" t="n">
-        <v>2.430976735467993e-07</v>
+        <v>0.0574260987341404</v>
       </c>
       <c r="X4" t="n">
-        <v>6.546089252879028e-07</v>
+        <v>0.08860432356595993</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.326121600366605e-07</v>
+        <v>0.03289204835891724</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.134043342039149e-07</v>
+        <v>0.1274276822805405</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.339029934883001e-07</v>
+        <v>0.007942089810967445</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.206289397259752e-07</v>
+        <v>0.019556924700737</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.880969080048089e-06</v>
+        <v>0.04514817520976067</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.623598251399017e-07</v>
+        <v>0.04265383630990982</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.801984126359457e-07</v>
+        <v>0.002970034256577492</v>
       </c>
       <c r="AF4" t="n">
-        <v>7.523869385295257e-07</v>
+        <v>0.07631924748420715</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.647708695098117e-07</v>
+        <v>0.02607394382357597</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.278223286746652e-08</v>
+        <v>0.07539687305688858</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.902425191881775e-07</v>
+        <v>0.03628862276673317</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.859727317172656e-07</v>
+        <v>0.1504424214363098</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.397294960905128e-07</v>
+        <v>0.01510121952742338</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.179244766395641e-08</v>
+        <v>0.1722227931022644</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.121802739589839e-07</v>
+        <v>0.03113405220210552</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.074315367892268e-07</v>
+        <v>0.1394742727279663</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.074318589644463e-07</v>
+        <v>0.152064323425293</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.389796807416133e-06</v>
+        <v>0.1196456030011177</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.453902823162935e-07</v>
+        <v>0.06922814249992371</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.917158946682321e-08</v>
+        <v>0.1048764586448669</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.626912246090797e-07</v>
+        <v>0.0004497412592172623</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.038795277163445e-07</v>
+        <v>0.02159329876303673</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.734402629466786e-07</v>
+        <v>0.28331658244133</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.643614609747601e-06</v>
+        <v>0.01889364048838615</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.705367367321742e-06</v>
+        <v>0.3924441337585449</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.11178791889688e-06</v>
+        <v>0.3082719743251801</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.00378495316545e-07</v>
+        <v>0.005722584202885628</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8.506920607942448e-07</v>
+        <v>0.004159535281360149</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.450498984922888e-06</v>
+        <v>0.03072375990450382</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.075186787602433e-06</v>
+        <v>0.1686071008443832</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.559387783345301e-06</v>
+        <v>0.01943820714950562</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.431489977221645e-06</v>
+        <v>0.02114345319569111</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.278073341381969e-06</v>
+        <v>0.03663679212331772</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.930091677124437e-07</v>
+        <v>0.0433700829744339</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.18665764148318e-06</v>
+        <v>0.03214577585458755</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.994509137963178e-07</v>
+        <v>0.1191423088312149</v>
       </c>
       <c r="BI4" t="n">
-        <v>7.202044116638717e-07</v>
+        <v>0.03363356739282608</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.866389518720098e-07</v>
+        <v>0.008458450436592102</v>
       </c>
       <c r="BK4" t="n">
-        <v>4.565092694974737e-07</v>
+        <v>0.2177461683750153</v>
       </c>
       <c r="BL4" t="n">
-        <v>2.349561043502035e-07</v>
+        <v>0.04061771184206009</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.26659176657995e-06</v>
+        <v>0.07937411963939667</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.427614447242377e-07</v>
+        <v>0.03670507296919823</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.594258603494382e-07</v>
+        <v>0.004392430186271667</v>
       </c>
       <c r="BP4" t="n">
-        <v>2.046711415459868e-06</v>
+        <v>0.1027294099330902</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.087912207571208e-07</v>
+        <v>0.08463203907012939</v>
       </c>
       <c r="BR4" t="n">
-        <v>1.256473751709564e-07</v>
+        <v>0.008771773427724838</v>
       </c>
       <c r="BS4" t="n">
-        <v>3.416844833736832e-07</v>
+        <v>0.0408572182059288</v>
       </c>
       <c r="BT4" t="n">
-        <v>1.754041363710712e-06</v>
+        <v>0.04384756460785866</v>
       </c>
       <c r="BU4" t="n">
-        <v>7.844828076031263e-08</v>
+        <v>8.036941289901733e-05</v>
       </c>
       <c r="BV4" t="n">
-        <v>3.578977612050949e-07</v>
+        <v>0.2398929595947266</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.094505475724873e-07</v>
+        <v>0.01803972013294697</v>
       </c>
       <c r="BX4" t="n">
-        <v>1.028271526593016e-06</v>
+        <v>0.3013890385627747</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.903344696074782e-06</v>
+        <v>0.05181837826967239</v>
       </c>
       <c r="BZ4" t="n">
-        <v>9.047837323805652e-08</v>
+        <v>0.06185906380414963</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.639384663576493e-07</v>
+        <v>0.05425183847546577</v>
       </c>
       <c r="CB4" t="n">
-        <v>1.359947987111809e-06</v>
+        <v>0.06367027759552002</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.148035870343847e-08</v>
+        <v>0.005712145939469337</v>
       </c>
       <c r="CD4" t="n">
-        <v>5.952971378064831e-07</v>
+        <v>0.04215195402503014</v>
       </c>
       <c r="CE4" t="n">
-        <v>6.660122409130054e-08</v>
+        <v>0.1534617990255356</v>
       </c>
       <c r="CF4" t="n">
-        <v>4.756593057209102e-07</v>
+        <v>0.01352622546255589</v>
       </c>
       <c r="CG4" t="n">
-        <v>8.052993507590145e-07</v>
+        <v>0.2537356615066528</v>
       </c>
       <c r="CH4" t="n">
-        <v>4.197068790290359e-07</v>
+        <v>0.03919798508286476</v>
       </c>
       <c r="CI4" t="n">
-        <v>6.508954015771451e-07</v>
+        <v>0.01502569392323494</v>
       </c>
       <c r="CJ4" t="n">
-        <v>6.36188417502126e-08</v>
+        <v>0.0006236238405108452</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.502197761737989e-07</v>
+        <v>0.08238247036933899</v>
       </c>
       <c r="CL4" t="n">
-        <v>5.101902047499607e-07</v>
+        <v>0.02609582990407944</v>
       </c>
       <c r="CM4" t="n">
-        <v>1.033846928066851e-07</v>
+        <v>0.002213563770055771</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.520961291134881e-06</v>
+        <v>0.1465746611356735</v>
       </c>
       <c r="CO4" t="n">
-        <v>2.047390808002092e-06</v>
+        <v>0.07477737963199615</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.410793061040749e-06</v>
+        <v>0.4250715374946594</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.026814854616532e-06</v>
+        <v>0.09228459000587463</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.179011064778024e-06</v>
+        <v>0.0006050616502761841</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.566059376680641e-07</v>
+        <v>0.01954448223114014</v>
       </c>
       <c r="CT4" t="n">
-        <v>1.527865947537066e-06</v>
+        <v>0.022723238915205</v>
       </c>
       <c r="CU4" t="n">
-        <v>6.661803695351409e-07</v>
+        <v>0.01440756022930145</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.634561440117977e-07</v>
+        <v>0.0441804826259613</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.230283714903635e-07</v>
+        <v>0.1516991406679153</v>
       </c>
       <c r="CX4" t="n">
-        <v>6.69558062327269e-07</v>
+        <v>0.03063412569463253</v>
       </c>
       <c r="CY4" t="n">
-        <v>7.377606721092889e-07</v>
+        <v>0.2592064738273621</v>
       </c>
       <c r="CZ4" t="n">
-        <v>3.205554435226077e-07</v>
+        <v>0.0255899541079998</v>
       </c>
       <c r="DA4" t="n">
-        <v>3.447643166509806e-07</v>
+        <v>0.01715357415378094</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.249556476068392e-07</v>
+        <v>0.02253764681518078</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.100000529026147e-07</v>
+        <v>0.07135292142629623</v>
       </c>
       <c r="DD4" t="n">
-        <v>6.110162757977378e-07</v>
+        <v>0.02122505754232407</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.432302383364004e-07</v>
+        <v>0.02384194731712341</v>
       </c>
       <c r="DF4" t="n">
-        <v>9.528210966891493e-07</v>
+        <v>0.189163863658905</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.743450918136659e-07</v>
+        <v>0.04635094106197357</v>
       </c>
       <c r="DH4" t="n">
-        <v>6.47278397991613e-07</v>
+        <v>0.1862483620643616</v>
       </c>
       <c r="DI4" t="n">
-        <v>4.322677796153584e-06</v>
+        <v>0.1663357317447662</v>
       </c>
       <c r="DJ4" t="n">
-        <v>3.338715032441542e-06</v>
+        <v>0.1091649308800697</v>
       </c>
       <c r="DK4" t="n">
-        <v>9.296702501160325e-07</v>
+        <v>0.01646316796541214</v>
       </c>
       <c r="DL4" t="n">
-        <v>4.679133382978762e-07</v>
+        <v>0.2858490943908691</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.749866328282224e-06</v>
+        <v>0.08819502592086792</v>
       </c>
       <c r="DN4" t="n">
-        <v>2.728415040564869e-07</v>
+        <v>0.004003673791885376</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.46747515827883e-06</v>
+        <v>0.05105933547019958</v>
       </c>
       <c r="DP4" t="n">
-        <v>3.243016806209198e-07</v>
+        <v>0.03424061462283134</v>
       </c>
       <c r="DQ4" t="n">
-        <v>6.153181288937049e-07</v>
+        <v>0.1365593373775482</v>
       </c>
       <c r="DR4" t="n">
-        <v>2.160970097975223e-06</v>
+        <v>0.05018800869584084</v>
       </c>
       <c r="DS4" t="n">
-        <v>4.382549718684459e-07</v>
+        <v>0.0317322351038456</v>
       </c>
       <c r="DT4" t="n">
-        <v>6.373917926794093e-07</v>
+        <v>0.1087603569030762</v>
       </c>
       <c r="DU4" t="n">
-        <v>6.617804615416389e-08</v>
+        <v>0.06394283473491669</v>
       </c>
       <c r="DV4" t="n">
-        <v>5.137164862389909e-07</v>
+        <v>0.2565697431564331</v>
       </c>
       <c r="DW4" t="n">
-        <v>9.616830709546775e-08</v>
+        <v>0.02452628687024117</v>
       </c>
       <c r="DX4" t="n">
-        <v>4.760192950925557e-07</v>
+        <v>0.03713389486074448</v>
       </c>
       <c r="DY4" t="n">
-        <v>4.173903676019108e-07</v>
+        <v>0.1039521470665932</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.168643954471918e-07</v>
+        <v>0.1374354958534241</v>
       </c>
       <c r="EA4" t="n">
-        <v>4.203778587452689e-07</v>
+        <v>0.1015274599194527</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.044925651034646e-08</v>
+        <v>0.01915836334228516</v>
       </c>
       <c r="EC4" t="n">
-        <v>3.114407149951148e-07</v>
+        <v>0.02855739928781986</v>
       </c>
       <c r="ED4" t="n">
-        <v>3.356685169819684e-07</v>
+        <v>0.2795907855033875</v>
       </c>
       <c r="EE4" t="n">
-        <v>5.61419483346981e-07</v>
+        <v>0.2116868644952774</v>
       </c>
       <c r="EF4" t="n">
-        <v>1.424276206307695e-06</v>
+        <v>0.1521307528018951</v>
       </c>
       <c r="EG4" t="n">
-        <v>5.470422479447734e-07</v>
+        <v>0.1368711143732071</v>
       </c>
       <c r="EH4" t="n">
-        <v>8.145574383888743e-07</v>
+        <v>0.06200144067406654</v>
       </c>
       <c r="EI4" t="n">
-        <v>7.77135937823914e-07</v>
+        <v>0.1958817392587662</v>
       </c>
       <c r="EJ4" t="n">
-        <v>3.283221872152353e-07</v>
+        <v>0.03146377205848694</v>
       </c>
       <c r="EK4" t="n">
-        <v>1.941311182918071e-07</v>
+        <v>0.0116641316562891</v>
       </c>
       <c r="EL4" t="n">
-        <v>3.99706152620638e-07</v>
+        <v>0.007872927933931351</v>
       </c>
       <c r="EM4" t="n">
-        <v>7.135938062674541e-07</v>
+        <v>0.0253742691129446</v>
       </c>
       <c r="EN4" t="n">
-        <v>1.086389829652035e-06</v>
+        <v>0.02544689737260342</v>
       </c>
       <c r="EO4" t="n">
-        <v>4.896883751825953e-07</v>
+        <v>0.06460054218769073</v>
       </c>
       <c r="EP4" t="n">
-        <v>8.579757349025385e-08</v>
+        <v>0.1424526274204254</v>
       </c>
       <c r="EQ4" t="n">
-        <v>7.702642506046686e-07</v>
+        <v>0.05647183954715729</v>
       </c>
       <c r="ER4" t="n">
-        <v>2.079416162814596e-06</v>
+        <v>0.1386665999889374</v>
       </c>
       <c r="ES4" t="n">
-        <v>1.27943997085822e-06</v>
+        <v>0.04427492991089821</v>
       </c>
       <c r="ET4" t="n">
-        <v>2.681529167603003e-07</v>
+        <v>0.09621511399745941</v>
       </c>
       <c r="EU4" t="n">
-        <v>7.120269174265559e-08</v>
+        <v>0.0814189612865448</v>
       </c>
       <c r="EV4" t="n">
-        <v>6.664475336037867e-07</v>
+        <v>0.123842254281044</v>
       </c>
       <c r="EW4" t="n">
-        <v>3.873797140840907e-07</v>
+        <v>0.06366392225027084</v>
       </c>
       <c r="EX4" t="n">
-        <v>4.860827971242543e-07</v>
+        <v>0.03368386998772621</v>
       </c>
       <c r="EY4" t="n">
-        <v>8.482800950559977e-08</v>
+        <v>0.1663967072963715</v>
       </c>
       <c r="EZ4" t="n">
-        <v>5.994270964038151e-07</v>
+        <v>0.005565397907048464</v>
       </c>
       <c r="FA4" t="n">
-        <v>5.741413247051241e-07</v>
+        <v>0.2970032691955566</v>
       </c>
       <c r="FB4" t="n">
-        <v>2.094244067052387e-08</v>
+        <v>0.03085491061210632</v>
       </c>
       <c r="FC4" t="n">
-        <v>3.3794478326854e-07</v>
+        <v>0.02180219441652298</v>
       </c>
       <c r="FD4" t="n">
-        <v>8.032287723835907e-08</v>
+        <v>0.009523786604404449</v>
       </c>
       <c r="FE4" t="n">
-        <v>3.106814858711004e-07</v>
+        <v>0.1091696918010712</v>
       </c>
       <c r="FF4" t="n">
-        <v>4.26162529265639e-07</v>
+        <v>0.01626669988036156</v>
       </c>
       <c r="FG4" t="n">
-        <v>8.294001929698425e-08</v>
+        <v>0.06651586294174194</v>
       </c>
       <c r="FH4" t="n">
-        <v>6.424638172575214e-07</v>
+        <v>0.08372640609741211</v>
       </c>
       <c r="FI4" t="n">
-        <v>6.910664751558215e-07</v>
+        <v>0.02838058583438396</v>
       </c>
       <c r="FJ4" t="n">
-        <v>4.326333282733685e-07</v>
+        <v>0.1258300691843033</v>
       </c>
       <c r="FK4" t="n">
-        <v>1.404224292400613e-08</v>
+        <v>0.02468702010810375</v>
       </c>
       <c r="FL4" t="n">
-        <v>7.764326710457681e-07</v>
+        <v>0.01091547124087811</v>
       </c>
       <c r="FM4" t="n">
-        <v>6.272711630117556e-07</v>
+        <v>0.05975835770368576</v>
       </c>
       <c r="FN4" t="n">
-        <v>1.444712296461148e-07</v>
+        <v>0.05720303580164909</v>
       </c>
       <c r="FO4" t="n">
-        <v>1.42351652243633e-07</v>
+        <v>0.129948616027832</v>
       </c>
       <c r="FP4" t="n">
-        <v>1.485344114371401e-07</v>
+        <v>0.0005693696439266205</v>
       </c>
       <c r="FQ4" t="n">
-        <v>6.085087989049498e-07</v>
+        <v>0.2923872470855713</v>
       </c>
       <c r="FR4" t="n">
-        <v>1.60546164806874e-06</v>
+        <v>0.08136270940303802</v>
       </c>
       <c r="FS4" t="n">
-        <v>1.715342477837112e-06</v>
+        <v>0.2985536456108093</v>
       </c>
       <c r="FT4" t="n">
-        <v>3.037955593754305e-06</v>
+        <v>0.04883316531777382</v>
       </c>
       <c r="FU4" t="n">
-        <v>7.892147095844848e-07</v>
+        <v>0.1373034864664078</v>
       </c>
       <c r="FV4" t="n">
-        <v>1.583947891958815e-06</v>
+        <v>0.04871192574501038</v>
       </c>
       <c r="FW4" t="n">
-        <v>5.122277570990263e-07</v>
+        <v>0.02632634155452251</v>
       </c>
       <c r="FX4" t="n">
-        <v>1.279042862734059e-06</v>
+        <v>0.2277177274227142</v>
       </c>
       <c r="FY4" t="n">
-        <v>4.650890730317769e-07</v>
+        <v>0.06584050506353378</v>
       </c>
       <c r="FZ4" t="n">
-        <v>2.977761539568746e-07</v>
+        <v>0.09027340263128281</v>
       </c>
       <c r="GA4" t="n">
-        <v>6.33200272659451e-07</v>
+        <v>0.01573734730482101</v>
       </c>
       <c r="GB4" t="n">
-        <v>1.270487700821832e-06</v>
+        <v>0.2268602550029755</v>
       </c>
       <c r="GC4" t="n">
-        <v>3.027333377758623e-06</v>
+        <v>0.100794717669487</v>
       </c>
       <c r="GD4" t="n">
-        <v>1.935099362526671e-06</v>
+        <v>0.09267240762710571</v>
       </c>
       <c r="GE4" t="n">
-        <v>1.577506907324278e-07</v>
+        <v>0.1494116187095642</v>
       </c>
       <c r="GF4" t="n">
-        <v>1.720401655802561e-06</v>
+        <v>0.08835212141275406</v>
       </c>
       <c r="GG4" t="n">
-        <v>6.758334052392456e-07</v>
+        <v>0.01304142735898495</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>0.003183080581948161</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.007316270843148232</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.760886076837778e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.0007335483096539974</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.000680751574691385</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.007524099200963974</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.002923810854554176</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.002348108217120171</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.001998909749090672</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.003367413999512792</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.009465483948588371</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.0008822442032396793</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.0007742647430859506</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.002198923379182816</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.006735773291438818</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.001700182096101344</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.0003423241432756186</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.003795052180066705</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.83708393201232e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.000161862320965156</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.00207634549587965</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.001563394675031304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.001325933379121125</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.001078926725313067</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>0.0005226632347330451</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>0.002140336204320192</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.000903745589312166</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>0.0001901853829622269</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.001329787424765527</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>0.001058690482750535</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>0.001369774574413896</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.002237554406747222</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>0.0006219603819772601</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>0.0002582072629593313</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>0.00353503949008882</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>0.0003768177120946348</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.000819895532913506</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.001073103048838675</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.001441413769498467</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>0.001662615686655045</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>0.0004024927329737693</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>0.0007244321750476956</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.001089795725420117</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.002571601420640945</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>0.001368232420645654</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>0.002634837757796049</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>0.007044631522148848</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.001463833963498473</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.0003109495737589896</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>0.001146580092608929</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>0.003948719706386328</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>0.0002271810808451846</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>0.001162708853371441</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>0.0009180918568745255</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>0.000537980580702424</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>0.001186474575661123</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>0.0006866562180221081</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>7.035309681668878e-05</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>0.001092127175070345</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>0.002612319076433778</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>0.0009655841859057546</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>0.001242653699591756</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>0.001274437410756946</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>0.0002178978465963155</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>0.001752693438902497</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>0.000339297839673236</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>8.178681309800595e-05</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>0.00176302227191627</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>0.001184635795652866</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>0.003105494193732738</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>0.0004317374259699136</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>0.001538712764158845</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>0.0009460059809498489</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>0.004142540507018566</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>0.001224156701937318</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>0.002486188430339098</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>7.225899025797844e-07</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>0.002378284931182861</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>0.0007846315274946392</v>
       </c>
       <c r="CB5" t="n">
-        <v>0</v>
+        <v>0.0008204574696719646</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>0.001125192851759493</v>
       </c>
       <c r="CD5" t="n">
-        <v>0</v>
+        <v>0.001396846608258784</v>
       </c>
       <c r="CE5" t="n">
-        <v>0</v>
+        <v>0.00212939502671361</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>0.0004769355291500688</v>
       </c>
       <c r="CG5" t="n">
-        <v>0</v>
+        <v>0.0004322427557781339</v>
       </c>
       <c r="CH5" t="n">
-        <v>0</v>
+        <v>0.0008906826260499656</v>
       </c>
       <c r="CI5" t="n">
-        <v>0</v>
+        <v>0.001860248041339219</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>0.001302794087678194</v>
       </c>
       <c r="CK5" t="n">
-        <v>0</v>
+        <v>0.0003101764887105674</v>
       </c>
       <c r="CL5" t="n">
-        <v>0</v>
+        <v>0.0001963625254575163</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>0.0006474168039858341</v>
       </c>
       <c r="CN5" t="n">
-        <v>0</v>
+        <v>0.003714888356626034</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>0.001556808012537658</v>
       </c>
       <c r="CP5" t="n">
-        <v>0</v>
+        <v>0.001449308823794127</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0</v>
+        <v>0.002208126941695809</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>0.001152904704213142</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>0.0005849648732692003</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>0.0008832167368382215</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>0.0002678402233868837</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>0.001027449266985059</v>
       </c>
       <c r="CW5" t="n">
-        <v>0</v>
+        <v>0.001947922981344163</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>0.0003569637192413211</v>
       </c>
       <c r="CY5" t="n">
-        <v>0</v>
+        <v>0.0002854567137546837</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0</v>
+        <v>0.0007157331565394998</v>
       </c>
       <c r="DA5" t="n">
-        <v>0</v>
+        <v>0.001806894084438682</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>0.0006749320309609175</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>0.0005080223199911416</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>0.0003741756663657725</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>0.0006262516835704446</v>
       </c>
       <c r="DF5" t="n">
-        <v>0</v>
+        <v>0.002339315135031939</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>0.001639614696614444</v>
       </c>
       <c r="DH5" t="n">
-        <v>0</v>
+        <v>0.0003380576381459832</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>0.002917947946116328</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>0.003479387145489454</v>
       </c>
       <c r="DK5" t="n">
-        <v>0</v>
+        <v>0.0001918512862175703</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>0.002018511295318604</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>0.0009843176230788231</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>0.0006082397885620594</v>
       </c>
       <c r="DO5" t="n">
-        <v>0</v>
+        <v>0.001263221958652139</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>0.0008298695902340114</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0</v>
+        <v>0.001654628315009177</v>
       </c>
       <c r="DR5" t="n">
-        <v>0</v>
+        <v>0.0006618136540055275</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.002100462792441249</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>0.0005968118784949183</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>0.002476949244737625</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>0.0005175197729840875</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>0.0009720373200252652</v>
       </c>
       <c r="DX5" t="n">
-        <v>0</v>
+        <v>0.0001934947213158011</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>0.0002173000248149037</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>0.0009428788907825947</v>
       </c>
       <c r="EA5" t="n">
-        <v>0</v>
+        <v>0.001077406108379364</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>0.002188899554312229</v>
       </c>
       <c r="EC5" t="n">
-        <v>0</v>
+        <v>8.027933654375374e-05</v>
       </c>
       <c r="ED5" t="n">
-        <v>0</v>
+        <v>0.001421891036443412</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>0.002407776191830635</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>0.001273593166843057</v>
       </c>
       <c r="EG5" t="n">
-        <v>0</v>
+        <v>4.275801620678976e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>0</v>
+        <v>0.001397711574099958</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>4.357931902632117e-05</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0</v>
+        <v>0.001363931223750114</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>0.001197786652483046</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>0.0008856632630340755</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>0.0002877357765100896</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>3.155707963742316e-05</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>0.00125518802087754</v>
       </c>
       <c r="EP5" t="n">
-        <v>0</v>
+        <v>0.0007573890034109354</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>0.0002038393868133426</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>0.001003693789243698</v>
       </c>
       <c r="ES5" t="n">
-        <v>0</v>
+        <v>0.002360451966524124</v>
       </c>
       <c r="ET5" t="n">
-        <v>0</v>
+        <v>0.002325112232938409</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>0.0004143698315601796</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>0.0003688669239636511</v>
       </c>
       <c r="EW5" t="n">
-        <v>0</v>
+        <v>0.001048492500558496</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>0.001231111353263259</v>
       </c>
       <c r="EY5" t="n">
-        <v>0</v>
+        <v>0.002470636973157525</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0</v>
+        <v>0.0002185926859965548</v>
       </c>
       <c r="FA5" t="n">
-        <v>0</v>
+        <v>0.0002118330448865891</v>
       </c>
       <c r="FB5" t="n">
-        <v>0</v>
+        <v>0.001318300957791507</v>
       </c>
       <c r="FC5" t="n">
-        <v>0</v>
+        <v>0.001653544837608933</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>0.001180004444904625</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>0.0005146071198396385</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>0.0002189999941037968</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>0.0004122619866393507</v>
       </c>
       <c r="FH5" t="n">
-        <v>0</v>
+        <v>0.003054464934393764</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>0.001320401672273874</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0</v>
+        <v>0.0009656107285991311</v>
       </c>
       <c r="FK5" t="n">
-        <v>0</v>
+        <v>0.0004615483048837632</v>
       </c>
       <c r="FL5" t="n">
-        <v>0</v>
+        <v>0.002454869914799929</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>0.001147696282714605</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>0.003367573022842407</v>
       </c>
       <c r="FO5" t="n">
-        <v>0</v>
+        <v>0.001662056427448988</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>0.001175517681986094</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0</v>
+        <v>0.0002241618640255183</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>0.004246842116117477</v>
       </c>
       <c r="FS5" t="n">
-        <v>0</v>
+        <v>0.00224435911513865</v>
       </c>
       <c r="FT5" t="n">
-        <v>0</v>
+        <v>0.0004809790989384055</v>
       </c>
       <c r="FU5" t="n">
-        <v>0</v>
+        <v>0.0003426647162996233</v>
       </c>
       <c r="FV5" t="n">
-        <v>0</v>
+        <v>0.0006134929717518389</v>
       </c>
       <c r="FW5" t="n">
-        <v>0</v>
+        <v>0.001857900759205222</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>0.001483990694396198</v>
       </c>
       <c r="FY5" t="n">
-        <v>0</v>
+        <v>0.001812808099202812</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0</v>
+        <v>0.001377924345433712</v>
       </c>
       <c r="GA5" t="n">
-        <v>0</v>
+        <v>0.001026118639856577</v>
       </c>
       <c r="GB5" t="n">
-        <v>0</v>
+        <v>0.000649980443995446</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>0.00295588537119329</v>
       </c>
       <c r="GD5" t="n">
-        <v>0</v>
+        <v>0.002245285548269749</v>
       </c>
       <c r="GE5" t="n">
-        <v>0</v>
+        <v>0.000425296020694077</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>0.001655607484281063</v>
       </c>
       <c r="GG5" t="n">
-        <v>0</v>
+        <v>0.002333857351914048</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.4940350353717804</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7101423740386963</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04687840491533279</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0904170423746109</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1339467763900757</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.240440309047699</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.06150612607598305</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2325134873390198</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1396118849515915</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5906184911727905</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6674399375915527</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.128626823425293</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.08761195093393326</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4283020794391632</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.130845308303833</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1028970256447792</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.1902876347303391</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3510219156742096</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.01452620048075914</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.00366006582044065</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.1255797147750854</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.08463481068611145</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.008580222725868225</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.0648130401968956</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.01332667842507362</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1848983466625214</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1414489150047302</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.09821009635925293</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1590735614299774</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.02019686251878738</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.05306286737322807</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1398496478796005</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.05876050889492035</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.02751503512263298</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.04309377446770668</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.0475970059633255</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.1243811771273613</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2504065036773682</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.2187509834766388</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.1080628633499146</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.1106851324439049</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.01644031330943108</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.06386943906545639</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.0002716053277254105</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.07078095525503159</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.3314913511276245</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.1787591874599457</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.06600193679332733</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.0695691779255867</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.3103905916213989</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.01235933974385262</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.02822813205420971</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.004946842789649963</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.05034060031175613</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.1006233915686607</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.1850026696920395</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.1215922459959984</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.08365726470947266</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.005089104175567627</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.2924370765686035</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.02202277258038521</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.05629504099488258</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.1515088528394699</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.08293400704860687</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.1019122451543808</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.03937346860766411</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.06810767203569412</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.02519454434514046</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.1545569002628326</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.03944505751132965</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.09070651233196259</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.02481769025325775</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.2043318152427673</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.1982671320438385</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.1309401094913483</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.1426532119512558</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.0747971385717392</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.1012308597564697</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.04130531847476959</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.09725221246480942</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.1501973122358322</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.1726012825965881</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.2253141701221466</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.05624466016888618</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.04114985466003418</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.0229504182934761</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.08436170965433121</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.05431855469942093</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.04977724328637123</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.01764386333525181</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.2002710402011871</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.1731923073530197</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.1447438895702362</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.2628819644451141</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.05139023065567017</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.2416063249111176</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.03626364842057228</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.01718540489673615</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0.07215838879346848</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.1770023256540298</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.2100012749433517</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.04659844934940338</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.03610417246818542</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.006681495811790228</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.08035391569137573</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.06760965287685394</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.08659059554338455</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.004017774015665054</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.09832675755023956</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.1642290353775024</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.0456988513469696</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.02434326894581318</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.3029102385044098</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.1613287776708603</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0.01248498633503914</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.06380867213010788</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.1781670749187469</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.08670565485954285</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.1278193593025208</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0.03019767254590988</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.06505881249904633</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.05018972977995872</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.2254880666732788</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.08771789073944092</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.2218627482652664</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0.005176360253244638</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.08029229193925858</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.01580778881907463</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0.0557778999209404</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.09860201925039291</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.3046011030673981</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.2936099767684937</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0.1657721251249313</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.1549785733222961</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0.1814830899238586</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0.0718112513422966</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0.08360184729099274</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0.1670499294996262</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.01250400766730309</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.03727428615093231</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.0803290456533432</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0.02762163616716862</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.02529784850776196</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0.07228947430849075</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0.2030210494995117</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.1806090176105499</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0.1835194677114487</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0.05393197387456894</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.07803181558847427</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.13666732609272</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0.03643381595611572</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0.1166548132896423</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0.2588421404361725</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0.2071745246648788</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.2331634759902954</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0.02962655015289783</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.04704121872782707</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.02498931810259819</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.05328754335641861</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0.04350009188055992</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0.1035603880882263</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0.0305657684803009</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0.05087784677743912</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.2139256000518799</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0.09112140536308289</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.06333234906196594</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.09367417544126511</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.063912034034729</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0.13111911714077</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0.2169378101825714</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0.1431758850812912</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0.1800752729177475</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.2799609899520874</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0.2686277627944946</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.2109274566173553</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.2419793754816055</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.1039960533380508</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0.139414370059967</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0.165105864405632</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0.03690744191408157</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.1894040554761887</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.03957699984312057</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.03166394308209419</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0.08181140571832657</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.004951023031026125</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.00361379818059504</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0.03129507601261139</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0.1252712905406952</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.3187848031520844</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.02309456095099449</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.2734729945659637</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.09609118849039078</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.01456516981124878</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1077111810445786</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3942102491855621</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.06572874635457993</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1572389304637909</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01327582914382219</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.007921518757939339</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3305842280387878</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1230879798531532</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.04739105701446533</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.01801797747612</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.384534627199173</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.01166075840592384</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.04101767018437386</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.04177926480770111</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.004115271382033825</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.05087931454181671</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.02643650025129318</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1430602967739105</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.08490924537181854</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.01009139139205217</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.005782311782240868</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.0001353160478174686</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01807051710784435</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.03261443972587585</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.007273043505847454</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.05310046672821045</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.1196888983249664</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.09204018115997314</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.06809686124324799</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.04324563592672348</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.2001353800296783</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.0536414310336113</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0010643620043993</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.06656021624803543</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.005787499714642763</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.1042058765888214</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.01622874289751053</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.03679086267948151</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.01544718444347382</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.1012439876794815</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.02793076820671558</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.02410513907670975</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.343298614025116</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.1019388288259506</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.04776819795370102</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.04722742363810539</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.1682093739509583</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.08251300454139709</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.03208224102854729</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.03468944132328033</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0007109884172677994</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.06158963218331337</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.02970650047063828</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.03794757276773453</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.03185338899493217</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.08018261194229126</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.05455277860164642</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.03821130469441414</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.02394732460379601</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.02715778537094593</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.06209032982587814</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.02111583203077316</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.06027331575751305</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.004999831318855286</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.1203814595937729</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.08033941686153412</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.06023920699954033</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.06688696891069412</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.02093188092112541</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2604627907276154</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.01869902759790421</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.1971342712640762</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.01616735383868217</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.1225632503628731</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.02594146877527237</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.01765700243413448</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.06065982580184937</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.002230326645076275</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.08556301146745682</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.01474176719784737</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.0335102304816246</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.03868971019983292</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.09303668141365051</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.01501574646681547</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.03018759936094284</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.004600259941071272</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.04295380786061287</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.12862229347229</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.03714753687381744</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.04082269966602325</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.1003711447119713</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0100400447845459</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>0.04944898933172226</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.06981028616428375</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.05333903059363365</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>0.01200451608747244</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.077593594789505</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0.02803300693631172</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.02857538498938084</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.02302911505103111</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.09110376983880997</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>0.008505316451191902</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.02075673267245293</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.003515604417771101</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0003102165646851063</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.1162442117929459</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.01555505394935608</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.04260819032788277</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.02870330214500427</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.1714540719985962</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.03781455010175705</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.1046973168849945</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0.1622514128684998</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.03264328464865685</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.06006533280014992</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.02564992383122444</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.1028135269880295</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.02466706372797489</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.004565563052892685</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.001881856471300125</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.009297110140323639</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.02895734459161758</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.05322835221886635</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.004838269203901291</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.08498455584049225</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.02370837330818176</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.007534006610512733</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.0640956312417984</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.001734113204292953</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.005357332527637482</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.1165172457695007</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.002042687498033047</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.04799892008304596</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.02930063381791115</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.02275597304105759</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.06844663619995117</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.008187604136765003</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0.01948736794292927</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.01605463214218616</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.009522795677185059</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.001053283922374249</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.04916918277740479</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.01311252266168594</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.066036656498909</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.1019735336303711</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.1330839395523071</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.02139569818973541</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0.02407108433544636</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.04925211519002914</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.006667670793831348</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.09735269099473953</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>0.01908642053604126</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.02967865951359272</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>0.036844152957201</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.09563495218753815</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.0245777927339077</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.0156987626105547</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>0.02733293548226357</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>0.02217775583267212</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.07549305260181427</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.06289766728878021</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.04485724121332169</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>0.03212038055062294</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.06108409538865089</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0.03766196593642235</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.1522356271743774</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.09051672369241714</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.0006545744836330414</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.05581207945942879</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.01835739240050316</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.1130364686250687</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.163384422659874</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.05601660907268524</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.1034693419933319</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.2326982915401459</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.07769553363323212</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.04202203452587128</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>0.02680730633437634</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.09306939691305161</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.0065125348046422</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0.1221128702163696</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.07524581253528595</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.02852697670459747</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0.002169773913919926</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.02741662226617336</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0.04159318655729294</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.8454703092575073</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2439196109771729</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3261065483093262</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.08221182972192764</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2345816045999527</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.104609340429306</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.06336629390716553</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1736356765031815</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.03970491513609886</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.9027422070503235</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2773497104644775</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4158324897289276</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2406398355960846</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.1096492782235146</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1679411828517914</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1189678013324738</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1703456193208694</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.00289936363697052</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1451903134584427</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.04083751514554024</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.04789085313677788</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.04332494735717773</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1624408662319183</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.07645399123430252</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.06145173311233521</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.04853086546063423</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.08940403163433075</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.01717233657836914</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.1342904567718506</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.019123874604702</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.05504454299807549</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.303064227104187</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.03913020342588425</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2334116548299789</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.05426686257123947</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.01450412161648273</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.3066630661487579</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.0310523509979248</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.01760130748152733</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.2991040647029877</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.1133936271071434</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.004906412214040756</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.07672706991434097</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.0864122062921524</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.1650669127702713</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.5170480608940125</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.07019491493701935</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.0958593487739563</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0.1745017915964127</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0.1434479951858521</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.0546359084546566</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0.05011680349707603</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0.09525489062070847</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0.04672785103321075</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.1152628213167191</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.2768400311470032</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0.1473323702812195</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0.2140888273715973</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0.08112908154726028</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0.0150327468290925</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.1057724878191948</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.125424861907959</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.0466599129140377</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.1979708820581436</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.09826762974262238</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.024697195738554</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.07835954427719116</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0.001435061451047659</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0.1082788780331612</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0.1315555274486542</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0.05622987821698189</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0.0250554122030735</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.4676010608673096</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0.01887920871376991</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0.1475630551576614</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0.02698641456663609</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0.155889019370079</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0.02384230121970177</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0.05669796839356422</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0.05475236847996712</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0.009925205260515213</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.3398514091968536</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.02961138263344765</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0.1105577722191811</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.004280160181224346</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.07390277087688446</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.05413117632269859</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.01492266822606325</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.007248238194733858</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0.01905438303947449</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0.2159858494997025</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0.3034837245941162</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0.3223202526569366</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.2145215570926666</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.1151688396930695</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0.06076237931847572</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0.07351550459861755</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0.04263097420334816</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0.01243406347930431</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0.3238657116889954</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0.06514430791139603</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0.1057952418923378</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0.03815841674804688</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.07324203103780746</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0.04289451986551285</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.003502749837934971</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0.06206859648227692</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0.1140382438898087</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0.2067974656820297</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0.02699544280767441</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0.09049411118030548</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.1533472090959549</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.2715693712234497</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0.1346516013145447</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.2357054948806763</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0.1046423017978668</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.0536041259765625</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0.1287829577922821</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0.06242027878761292</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.1026706099510193</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.03380655497312546</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0.0543096624314785</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0.1023559048771858</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0.1092114374041557</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0.1156490668654442</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0.09883970022201538</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0.09300816059112549</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0.1070953458547592</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0.06438305974006653</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.05264642462134361</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0.06371834129095078</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0.1102396547794342</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0.252086728811264</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0.3573900163173676</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0.05592094361782074</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0.2373126894235611</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0.1154175400733948</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0.04816955327987671</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0.1164184808731079</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.09569475799798965</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0.01121625211089849</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0.06719978898763657</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0.04799355939030647</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0.09361947327852249</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0.2647146880626678</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0.02824342623353004</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0.08118107169866562</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0.007884395308792591</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.007426441181451082</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0.03291767835617065</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0.1115103363990784</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0.09906351566314697</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0.03297387063503265</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0.3423592448234558</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0.04881454631686211</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0.1539712995290756</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0.0005535156815312803</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.06973127275705338</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0.04367328435182571</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0.003273393027484417</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0.06176648661494255</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0.01614542119204998</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0.1942126154899597</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0.06740637123584747</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0.1774175763130188</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.01585188508033752</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.04734712466597557</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0.08568795025348663</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0.0473397858440876</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0.01405675243586302</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0.07828500866889954</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.3464975357055664</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0.06094692647457123</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0.1798947900533676</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0.05867988616228104</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0.1270593702793121</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0.09498769789934158</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0.1488166302442551</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0.1322440803050995</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0.1088930740952492</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0.228361189365387</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0.06590884178876877</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0.04562133550643921</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0.08675609529018402</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.03266376629471779</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0.05480404943227768</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0.019442955031991</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0.07581794261932373</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9.753427576697504e-08</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5.928852964132147e-09</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.321607485901495e-09</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.737505486853479e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.478617672745486e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.917592733022502e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.644082558982518e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.816267136689476e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.058517788507743e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.431164851188441e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.701044721220569e-09</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.147215986767151e-08</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.96131857421733e-08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>7.415106040298269e-08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.890956179475324e-08</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6.485819170620744e-08</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.71387046776772e-08</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8.505161019911611e-08</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.952852705741861e-08</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.054439462995106e-08</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.659045688664264e-08</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.785085584378066e-08</v>
+      </c>
+      <c r="W11" t="n">
+        <v>9.847507698168556e-09</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.677683592049561e-08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.985279673988316e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.093957102682452e-08</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.635791946341669e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>7.339685481611014e-08</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.675083183272363e-08</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>6.35967367657031e-08</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>4.215542759311575e-08</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.884636979809784e-08</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.611463495976295e-08</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>6.220442116955383e-08</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.421543143782401e-08</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>6.627680626536403e-09</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>6.75934828109348e-08</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.705760865888806e-08</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.93041600482502e-08</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>8.750664193257762e-09</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>6.656181739117528e-08</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.037955937339575e-08</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3.958674277271257e-09</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.323183695944863e-08</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.017672346392828e-08</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.70301415589347e-08</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.103870914676008e-07</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.258793602687547e-08</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.028686025250636e-08</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5.237892253262544e-08</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.638979961806399e-08</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.964300544443631e-08</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.180275041207551e-09</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.57125743527331e-08</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5.025699323368826e-08</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>8.570970777554976e-08</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.875832467135297e-08</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.000296663278277e-07</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>3.38338779215519e-08</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>7.812992919298267e-08</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.58878785075467e-08</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>2.355002592935307e-08</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>4.481258475408367e-09</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1.280318961960347e-08</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.956589379403795e-08</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>2.617638372726105e-08</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>6.916006434209976e-09</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>6.450620038123134e-09</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>5.326184648879462e-08</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>4.688225629934095e-08</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>4.909837425515207e-09</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>2.181122482625142e-08</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.059047770648249e-08</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>3.154350025624808e-08</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>1.088486989431203e-08</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>3.076500831866724e-08</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>3.970200523895073e-08</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>5.905971267594623e-09</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>7.62016938438137e-09</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>3.441098783696361e-08</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>3.708455764694918e-08</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>3.293649442071001e-08</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>9.324528704723889e-09</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>4.59619897696939e-10</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>4.377889162299198e-09</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>2.00576373288186e-08</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>1.39251019604103e-08</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1.20169909578749e-08</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>3.832192341235441e-09</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>8.650044236446774e-09</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>8.027635800544886e-08</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>1.322108200696448e-08</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.387615533587905e-08</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>2.887682093444255e-08</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>9.870608153050853e-08</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>3.091810896194147e-08</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>2.192799897215991e-08</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>5.940125724634981e-09</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>2.769736262564493e-08</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>3.358245947993055e-08</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>5.201866493109719e-09</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>7.68826069474926e-09</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>1.547224570686012e-09</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>1.855272202533342e-08</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>9.479558471525706e-09</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>6.25583052027423e-09</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>1.360229973101923e-08</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1.006894123634083e-08</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>6.921862194531059e-08</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>9.313831483837021e-09</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.839960799860819e-08</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>3.971567075211624e-09</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>4.879137804891798e-08</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>4.27028510330274e-08</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>5.170275230170773e-08</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>6.841776212240802e-08</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>8.058889022777294e-08</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>6.353040049589254e-08</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>5.656103496676224e-08</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>1.742693633843828e-08</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>4.004131426427193e-08</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>6.102105487570952e-10</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>6.148935227656693e-08</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>1.350222600393636e-09</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>1.121826187500119e-08</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>1.568652052696962e-08</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>2.251133501829372e-08</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>3.371281920294678e-09</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>1.943803162873792e-08</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>3.665034853383986e-08</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>1.074947704182705e-07</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>2.971423818109997e-08</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>2.547416677600722e-08</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>5.157393179189285e-09</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>3.00063218716673e-09</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>4.384022389558595e-08</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>4.637773898252817e-08</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>2.205735860627556e-08</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>1.381063086114409e-08</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>1.569262053635612e-08</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>1.157953377628473e-08</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>1.827061169024091e-09</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>4.151431198806677e-08</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>1.249039005557506e-08</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>9.709676618285812e-09</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>3.034708839777522e-08</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>2.371600160699927e-08</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>1.911869418336209e-08</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>4.868870195906538e-09</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>3.506733392555361e-08</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>4.27581205997285e-08</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>9.88745263441615e-09</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>1.928492210367949e-08</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>4.083037907776088e-08</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>3.251341418319953e-09</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>3.093731049119697e-09</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>1.161087048728859e-08</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>1.113345149406086e-08</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>1.474299526904588e-08</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>1.26816193102286e-08</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>1.254668369199408e-08</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>3.602514953016112e-09</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>1.243677782980512e-08</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>2.052835768040495e-08</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>7.06822049778566e-08</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>4.054460234215185e-08</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>2.029825729721324e-08</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>4.609553183598791e-09</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>6.553646514362299e-10</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>9.786252697097098e-09</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>3.275260596069529e-08</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>1.166918650596926e-07</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>1.350105094388709e-08</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>1.131737690229784e-07</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>1.532177975605009e-07</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>1.103880542530078e-08</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>5.82400900839275e-08</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>7.823940606499491e-09</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>6.628076931747273e-08</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>2.467619353296868e-08</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>4.600763503503913e-08</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>2.840195634234988e-08</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>1.825296536139831e-08</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>6.394003548848559e-09</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>3.686521310442004e-08</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>3.089354194685257e-08</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>8.851245070218283e-09</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>3.010433147210279e-08</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>1.330199417282074e-08</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0.0003494736738502979</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.00193136534653604</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0008042906993068755</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.001042861025780439</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0004712298687081784</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.00078891112934798</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.000415007583796978</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0004207062302157283</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.287488157686312e-05</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0004947042907588184</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.001892098225653172</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.001008028630167246</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.001782099832780659</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.091390630695969e-05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0004249954072292894</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.0003841900906991214</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001861801720224321</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5.754756421083584e-05</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.683322888216935e-05</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.000221499809413217</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.0001115584309445694</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.000209828867809847</v>
+      </c>
+      <c r="W12" t="n">
+        <v>8.769483974901959e-05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.0003977238957304507</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.0001315549598075449</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.03667625808157e-05</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.0003397985128685832</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.0002724011137615889</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.000368579727364704</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.0003113224811386317</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0.0001713629462756217</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.000499482499435544</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.0007387053919956088</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.0002386151609243825</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.000204201161977835</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>5.670708196703345e-05</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.523291914258152e-05</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.0006055396515876055</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.0004669955233111978</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.0003424661117605865</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.0005820231162942946</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.0004793101688846946</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.0002040308900177479</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.099848618148826e-05</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.0002341712679481134</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0.0002670557878445834</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0.001208892557770014</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.0002346313995076343</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.0006103620398789644</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.0001653845829423517</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0.0002973817754536867</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.080881990375929e-05</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0.000155688903760165</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0.0003084084019064903</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6.364216824294999e-05</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0.0001883325167000294</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0.0003527557128109038</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>8.063935820246115e-05</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0.0002163401222787797</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>0.0002718680480029434</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0.0001250088971573859</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.0001231820933753625</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>3.170865238644183e-05</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>2.484292963345069e-05</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>8.100990089587867e-05</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>0.0003222205850761384</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.001992834266275e-05</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>4.492117659538053e-05</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>0.0003327456652186811</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0.0001123351394198835</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0.0002311608986929059</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1.634533327887766e-05</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>0.000157788279466331</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.0005718255997635424</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>0.0002921808918472379</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0.000571147829759866</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>0.000193599218619056</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0.0005820805672556162</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0.0001096646301448345</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>0.0001075937034329399</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0.0002116000396199524</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>8.125030581140891e-05</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.0006528268568217754</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.0002530204365029931</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.0004064316162839532</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.0002175488625653088</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.0001806292275432497</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>4.810466271010228e-05</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.0001162249463959597</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>5.146917828824371e-05</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>4.927369445795193e-05</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>0.0002432097971905023</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.0004281671717762947</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>0.0006602617213502526</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.0002876836515497416</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.0001578675874043256</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0.0002929148613475263</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>5.317650357028469e-05</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>0.0001139462401624769</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0.0001127924333559349</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>0.0006287076976150274</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0.0002283930080011487</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0.0004365955828689039</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>4.419734614202753e-05</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.000229500699788332</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>4.407413507578894e-05</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0.0001408965763403103</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>8.934113429859281e-05</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.000163872551638633</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>0.000585049856454134</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0.0004010568372905254</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0.0003039778966922313</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>2.378180215600878e-05</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.001215160125866532</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0.0001284259924432263</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.00073722202796489</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>0.0004179943643976003</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>7.16305075911805e-05</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>0.0004909156123176217</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>0.0002933217328973114</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0.000116559283924289</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0.0001736520644044504</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.0002909270115196705</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>4.744257603306323e-05</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>7.952822488732636e-05</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>0.0005064159631729126</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>8.005022391444072e-05</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>6.290210876613855e-06</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0.0004304570611566305</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>4.675857053371146e-05</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.0003194499004166573</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.0002910757903009653</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>0.0001260670542251319</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0.0007452257559634745</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>0.0006151929846964777</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>0.000109259519376792</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>0.0007823702180758119</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>9.033575770445168e-05</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0.00039172891410999</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>1.826449442887679e-05</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>7.63833595556207e-05</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>6.48363638902083e-05</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>4.870386692346074e-05</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>4.123597318539396e-05</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>0.0001072374434443191</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>0.0003713058831635863</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>7.339974399656057e-05</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>0.0003377023385837674</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>0.0001171094918390736</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.0001457965117879212</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>0.0002376227348577231</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>0.0001549090375192463</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0.0002714534639380872</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>0.0001230972993653268</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>0.0007721289293840528</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0.0002293973811902106</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0.0004637974197976291</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>0.0001180745603051037</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.0002809181460179389</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>1.716706901788712e-05</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0.0001935684413183481</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>7.855233707232401e-05</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>0.0001002947392407805</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>0.0002467301092110574</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>1.182712003355846e-05</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>0.0004198373353574425</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.000529969169292599</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>0.0003239226352889091</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0.0001261578436242417</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>7.569778972538188e-06</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>3.987991658505052e-05</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>0.0002973441442009062</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>0.0007635817164555192</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>3.04170825984329e-05</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>6.127091182861477e-05</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.0001909458806039765</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.0003418565611355007</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>0.0002393039176240563</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>7.448156975442544e-05</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>0.0006337424274533987</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>4.852643178310245e-05</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>0.0003553547139745206</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0.0003491908137220889</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>0.0001884135999716818</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>0.0002949405752588063</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>0.0001128456351580098</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>0.0002841171808540821</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0.0002931910566985607</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0.000109170432551764</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.04606419429183006</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.003348800353705883</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03341511636972427</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.004025829955935478</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.004320818930864334</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.04302346706390381</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.004120904020965099</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02131956815719604</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01675085723400116</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0477394126355648</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01687920466065407</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.04541216045618057</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.02296044491231441</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0185459777712822</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06464380770921707</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.009269217029213905</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.01186066493391991</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.02472237683832645</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.005613356828689575</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.01276294980198145</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.01413784548640251</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.003411917947232723</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.003645858028903604</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.0008855279302224517</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.02085196971893311</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.00243498245254159</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.001474449876695871</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.006088920868933201</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.002153716515749693</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.01054294686764479</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.01163140870630741</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.01656284928321838</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.002969660330563784</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.01419007126241922</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.005141391884535551</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.01156683079898357</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.008274540305137634</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.006953799165785313</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>4.543550312519073e-05</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.003731120377779007</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.01258392818272114</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.002312172437086701</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.002250360557809472</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.008181069046258926</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.00146351708099246</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.008773605339229107</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.02152663841843605</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.02825151942670345</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.002747056540101767</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.0207210835069418</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.03725716471672058</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.003201212733983994</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.005965852178633213</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.002208920195698738</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.02083259262144566</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.02125787734985352</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.0005723265931010246</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.001118925400078297</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.02843339368700981</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.0107260849326849</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.004329868126660585</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.0007021606434136629</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.005904737394303083</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.007823052816092968</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.004550745710730553</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.02086888439953327</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.001178106060251594</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.01104887761175632</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.002549295546486974</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>8.774222806096077e-06</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.001855430193245411</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.005812479183077812</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.005480806808918715</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.006768292747437954</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.01224642898887396</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.0003867140039801598</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.008718022145330906</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.01848892867565155</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.01754536107182503</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.0007405632059089839</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.002600227016955614</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.01079525891691446</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.01422075647860765</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.01045301556587219</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.003778610145673156</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.003518206300213933</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.007551918737590313</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.002063607098534703</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.0002866705763153732</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.002268079435452819</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.005224925465881824</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.004595134872943163</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.004637949168682098</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.002206896897405386</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.02315555512905121</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.007331152446568012</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.004734175279736519</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.01721393130719662</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.002114314585924149</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.01208799798041582</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.01007525622844696</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.01168623939156532</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.003071008715778589</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.006335531361401081</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.01046576071530581</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.004817474167793989</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.0003166471724398434</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.002942587016150355</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.01357110124081373</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.02112662419676781</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.004871193785220385</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.02418074198067188</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.004411377944052219</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.008847297169268131</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.005033113993704319</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.01994978077709675</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.01065598800778389</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.007951370440423489</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.0005568591877818108</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.01286003924906254</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.0002185872872360051</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.009383453987538815</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.01442060805857182</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.01874527335166931</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.0008985152235254645</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.004858599975705147</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.0008871650788933039</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.01447285804897547</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.0209154449403286</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.04349097236990929</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.03607778623700142</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.01509766466915607</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.005871898028999567</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.0009888657368719578</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.006895071361213923</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.003443554043769836</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.01114812958985567</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.01015544775873423</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.002518096938729286</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.007219501305371523</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.004620645195245743</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.002985491650179029</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.0007930057472549379</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.003313574008643627</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.006353588774800301</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.02556031197309494</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.001967168878763914</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.009128028526902199</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.0006684692343696952</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.007966254837810993</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.01107673719525337</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.02577280625700951</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.003976856358349323</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.01081908866763115</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.01019180938601494</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.008950849995017052</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.003445216454565525</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.004811567720025778</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.01215383969247341</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.006536798551678658</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.001942975679412484</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.001351952785626054</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.01844370737671852</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.01119749993085861</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.008642526343464851</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.02087084390223026</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.01483325101435184</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.01083356328308582</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.01655671373009682</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.02569647319614887</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.01324581913650036</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.006566574797034264</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.01783468946814537</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.01779135316610336</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.02593257091939449</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.01006152294576168</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.01935798302292824</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.02718271501362324</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.007708956021815538</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.01291314233094454</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.009561119601130486</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.02178914286196232</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.01810315623879433</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.0005786099936813116</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.002883910201489925</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.001140823820605874</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.002911257790401578</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.03014122135937214</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.003597588511183858</v>
       </c>
     </row>
   </sheetData>
